--- a/data/trans_orig/P0802-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2007</t>
+          <t>Población según limitación a subir varios pisos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>404068</t>
+          <t>403447</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>433083</t>
+          <t>432304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>243491</t>
+          <t>243561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269483</t>
+          <t>268744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658838</t>
+          <t>659221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>698268</t>
+          <t>695265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>48611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23988</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47580</t>
+          <t>47158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53722</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86651</t>
+          <t>86257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29654</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>22897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321643</t>
+          <t>321916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345130</t>
+          <t>344600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329276</t>
+          <t>329310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351373</t>
+          <t>350821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>660058</t>
+          <t>660354</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>690571</t>
+          <t>691123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34560</t>
+          <t>33973</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31238</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57471</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27984</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>456306</t>
+          <t>456430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>486074</t>
+          <t>488018</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116525</t>
+          <t>115607</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138899</t>
+          <t>137504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>581169</t>
+          <t>579257</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>619769</t>
+          <t>618789</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40025</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65583</t>
+          <t>65860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35272</t>
+          <t>35212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59893</t>
+          <t>60313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91973</t>
+          <t>93572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>27815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23865</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47017</t>
+          <t>46026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>979239</t>
+          <t>975736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1031867</t>
+          <t>1031052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>551223</t>
+          <t>545611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>592757</t>
+          <t>590417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1542427</t>
+          <t>1538481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1607212</t>
+          <t>1611094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152102</t>
+          <t>151963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200568</t>
+          <t>200947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97205</t>
+          <t>97221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135195</t>
+          <t>137052</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>261295</t>
+          <t>262601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>319951</t>
+          <t>324373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45491</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74769</t>
+          <t>74478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>39309</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69574</t>
+          <t>68481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105190</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279961</t>
+          <t>280268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306598</t>
+          <t>307222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>430452</t>
+          <t>431143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>469506</t>
+          <t>469097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>721365</t>
+          <t>717515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>770053</t>
+          <t>766594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>30910</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54697</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67746</t>
+          <t>68015</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101315</t>
+          <t>102003</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105916</t>
+          <t>106004</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>148104</t>
+          <t>148581</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48875</t>
+          <t>46343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63646</t>
+          <t>63462</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>280119</t>
+          <t>280212</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292781</t>
+          <t>292622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>809938</t>
+          <t>811630</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>878367</t>
+          <t>877442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1097381</t>
+          <t>1096113</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1168364</t>
+          <t>1165902</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264555</t>
+          <t>264861</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322824</t>
+          <t>322719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269436</t>
+          <t>270302</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>331043</t>
+          <t>332715</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92938</t>
+          <t>93555</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>135457</t>
+          <t>133452</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94507</t>
+          <t>94091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137742</t>
+          <t>135814</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2771934</t>
+          <t>2773912</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2849998</t>
+          <t>2852628</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2543658</t>
+          <t>2546349</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2642446</t>
+          <t>2643706</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5345283</t>
+          <t>5349102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5471894</t>
+          <t>5471360</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>302565</t>
+          <t>299572</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>369695</t>
+          <t>368233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>528645</t>
+          <t>526778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>615066</t>
+          <t>614332</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>848933</t>
+          <t>846951</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>963193</t>
+          <t>957959</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101157</t>
+          <t>100723</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>144483</t>
+          <t>144069</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>186990</t>
+          <t>182690</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>245861</t>
+          <t>241263</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>300393</t>
+          <t>302991</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>370444</t>
+          <t>376670</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2012</t>
+          <t>Población según limitación a subir varios pisos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>363567</t>
+          <t>364108</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>394722</t>
+          <t>393920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>264716</t>
+          <t>262472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287243</t>
+          <t>287167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>635436</t>
+          <t>634585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>674374</t>
+          <t>674896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34660</t>
+          <t>36060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61766</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58011</t>
+          <t>56513</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93929</t>
+          <t>92661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12756</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31802</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>354840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>382844</t>
+          <t>382513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286808</t>
+          <t>287229</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>310868</t>
+          <t>311064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649374</t>
+          <t>651631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>688268</t>
+          <t>687611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47128</t>
+          <t>46640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37309</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45097</t>
+          <t>45308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77013</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23389</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>489890</t>
+          <t>492429</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>531467</t>
+          <t>533920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>172397</t>
+          <t>173552</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203653</t>
+          <t>203645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>674313</t>
+          <t>677077</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>728125</t>
+          <t>727977</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>60497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95252</t>
+          <t>95636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>32595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56621</t>
+          <t>58223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99618</t>
+          <t>99596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145456</t>
+          <t>143925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56601</t>
+          <t>54421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37584</t>
+          <t>39309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50019</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82849</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>913472</t>
+          <t>915935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>969032</t>
+          <t>971661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>621118</t>
+          <t>622456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>663132</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1554525</t>
+          <t>1551160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1624634</t>
+          <t>1621446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117936</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164017</t>
+          <t>164094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57962</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91681</t>
+          <t>93489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186820</t>
+          <t>186857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241313</t>
+          <t>244914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60587</t>
+          <t>60566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96580</t>
+          <t>97006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34321</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62186</t>
+          <t>61373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101912</t>
+          <t>102795</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145647</t>
+          <t>148475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>404735</t>
+          <t>403962</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>438329</t>
+          <t>438868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>481859</t>
+          <t>481496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>537087</t>
+          <t>533802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898009</t>
+          <t>898410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>964819</t>
+          <t>959542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44488</t>
+          <t>44726</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74746</t>
+          <t>72254</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>124031</t>
+          <t>123063</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>168163</t>
+          <t>168557</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>175286</t>
+          <t>177307</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>228793</t>
+          <t>231158</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42794</t>
+          <t>42871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88262</t>
+          <t>89988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127956</t>
+          <t>127758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117262</t>
+          <t>117029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163944</t>
+          <t>161268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248259</t>
+          <t>247058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>261684</t>
+          <t>261215</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>685463</t>
+          <t>683445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>749152</t>
+          <t>749439</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>935749</t>
+          <t>938864</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1006749</t>
+          <t>1005578</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>222046</t>
+          <t>221830</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>277533</t>
+          <t>278468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>228794</t>
+          <t>228123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>288609</t>
+          <t>285583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118243</t>
+          <t>119891</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164647</t>
+          <t>166055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>125071</t>
+          <t>124780</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>172519</t>
+          <t>173443</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2841556</t>
+          <t>2833796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2933872</t>
+          <t>2921935</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2583348</t>
+          <t>2582940</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2694015</t>
+          <t>2689847</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5452945</t>
+          <t>5455665</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5596547</t>
+          <t>5595537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>320864</t>
+          <t>326140</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>397842</t>
+          <t>399243</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>523077</t>
+          <t>520873</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>613910</t>
+          <t>611318</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>864851</t>
+          <t>865899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>985398</t>
+          <t>981350</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>148830</t>
+          <t>147631</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>203517</t>
+          <t>203894</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>311435</t>
+          <t>310098</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>384735</t>
+          <t>380806</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>470446</t>
+          <t>478828</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>564820</t>
+          <t>567936</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2016</t>
+          <t>Población según limitación a subir varios pisos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>365385</t>
+          <t>366547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392128</t>
+          <t>392248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291589</t>
+          <t>293165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318889</t>
+          <t>318817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>666955</t>
+          <t>666966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>705718</t>
+          <t>704338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>24581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49049</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36239</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45094</t>
+          <t>44716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75889</t>
+          <t>76860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42686</t>
+          <t>43871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>322609</t>
+          <t>324120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347625</t>
+          <t>348720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311187</t>
+          <t>312349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339576</t>
+          <t>339052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>642469</t>
+          <t>643011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681292</t>
+          <t>681176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43470</t>
+          <t>44641</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72321</t>
+          <t>72364</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27307</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42662</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>424825</t>
+          <t>424278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456618</t>
+          <t>457520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109276</t>
+          <t>107318</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133905</t>
+          <t>132626</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>540205</t>
+          <t>540607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>581595</t>
+          <t>584369</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42695</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70422</t>
+          <t>70493</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43578</t>
+          <t>44871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69094</t>
+          <t>68798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105659</t>
+          <t>103861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36962</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28759</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>933192</t>
+          <t>931971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>982580</t>
+          <t>982912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>676436</t>
+          <t>676331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>717473</t>
+          <t>720445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1626004</t>
+          <t>1623803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1689692</t>
+          <t>1690394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109476</t>
+          <t>108511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152452</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>55446</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88189</t>
+          <t>86802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174572</t>
+          <t>173812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224477</t>
+          <t>230591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45568</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77340</t>
+          <t>78424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43636</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74938</t>
+          <t>74616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97520</t>
+          <t>97117</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139665</t>
+          <t>141359</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>471627</t>
+          <t>473894</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>514466</t>
+          <t>512568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>501768</t>
+          <t>502779</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>550335</t>
+          <t>553681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>991692</t>
+          <t>990046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1056855</t>
+          <t>1053701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72682</t>
+          <t>74044</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107604</t>
+          <t>107378</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107308</t>
+          <t>107892</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>149707</t>
+          <t>151625</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>190846</t>
+          <t>192166</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>245242</t>
+          <t>248906</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49384</t>
+          <t>48821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65692</t>
+          <t>63910</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102741</t>
+          <t>100315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97706</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139402</t>
+          <t>140556</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274289</t>
+          <t>273432</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285008</t>
+          <t>284939</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>711580</t>
+          <t>712468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>777860</t>
+          <t>780041</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>989195</t>
+          <t>992170</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1063137</t>
+          <t>1060407</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,45%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176613</t>
+          <t>178087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234339</t>
+          <t>233236</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181654</t>
+          <t>184277</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237658</t>
+          <t>238334</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110089</t>
+          <t>108000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159078</t>
+          <t>156252</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110935</t>
+          <t>111344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>158589</t>
+          <t>157284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2851148</t>
+          <t>2853013</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2932096</t>
+          <t>2934666</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2675941</t>
+          <t>2678696</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2780766</t>
+          <t>2781582</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5559257</t>
+          <t>5557376</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5694276</t>
+          <t>5687641</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>304157</t>
+          <t>301246</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>377579</t>
+          <t>373921</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>447209</t>
+          <t>447047</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>534172</t>
+          <t>533230</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>770039</t>
+          <t>770009</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>881201</t>
+          <t>874039</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132121</t>
+          <t>130947</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>181735</t>
+          <t>178352</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>280014</t>
+          <t>279182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>352450</t>
+          <t>355343</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>425608</t>
+          <t>426709</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>512367</t>
+          <t>516289</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2023</t>
+          <t>Población según limitación a subir varios pisos en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>449713</t>
+          <t>447631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>471203</t>
+          <t>470646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>382522</t>
+          <t>383857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>404584</t>
+          <t>404471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>837336</t>
+          <t>839928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>871313</t>
+          <t>870086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>40798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46030</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>54845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>78655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>23899</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387799</t>
+          <t>386411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412471</t>
+          <t>411438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316285</t>
+          <t>315260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337358</t>
+          <t>336599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709299</t>
+          <t>709011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742714</t>
+          <t>743576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31038</t>
+          <t>31939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53654</t>
+          <t>54399</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>48821</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66542</t>
+          <t>65086</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95753</t>
+          <t>96403</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24669</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37756</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124504</t>
+          <t>139639</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>557210</t>
+          <t>560359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112014</t>
+          <t>112748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>130613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>200413</t>
+          <t>218547</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>676895</t>
+          <t>675719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>70411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>536125</t>
+          <t>517410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>37224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104079</t>
+          <t>104069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>618041</t>
+          <t>598225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>44079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>21719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60939</t>
+          <t>60915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>807639</t>
+          <t>808709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>859477</t>
+          <t>860951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>814344</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>916390</t>
+          <t>907711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1639755</t>
+          <t>1640847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1780610</t>
+          <t>1791290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115814</t>
+          <t>115928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158586</t>
+          <t>158688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115219</t>
+          <t>114795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155386</t>
+          <t>152823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259779</t>
+          <t>259125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50526</t>
+          <t>49087</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>78934</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53614</t>
+          <t>53182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>69654</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>123865</t>
+          <t>123749</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>357674</t>
+          <t>357728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>393728</t>
+          <t>391972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>581442</t>
+          <t>577625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>681789</t>
+          <t>670738</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>952429</t>
+          <t>955644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1047861</t>
+          <t>1049803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51624</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>81177</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98292</t>
+          <t>100751</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160903</t>
+          <t>163361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>166514</t>
+          <t>164118</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>233310</t>
+          <t>229613</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25275</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>44728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64770</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105626</t>
+          <t>106654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98103</t>
+          <t>98918</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143314</t>
+          <t>143026</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>229229</t>
+          <t>228561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237960</t>
+          <t>238063</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>489076</t>
+          <t>485753</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>532855</t>
+          <t>529870</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>717293</t>
+          <t>717001</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>766375</t>
+          <t>768249</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137634</t>
+          <t>140599</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>172788</t>
+          <t>176001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144069</t>
+          <t>143492</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183708</t>
+          <t>182386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>82531</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>110755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81848</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111575</t>
+          <t>114137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2052193</t>
+          <t>2097795</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2873636</t>
+          <t>2875897</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2751442</t>
+          <t>2755702</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2958814</t>
+          <t>2958107</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4710050</t>
+          <t>4782299</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5710977</t>
+          <t>5699311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>344176</t>
+          <t>345671</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1204629</t>
+          <t>1155742</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>397148</t>
+          <t>398041</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>529710</t>
+          <t>533202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>818179</t>
+          <t>823198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1928430</t>
+          <t>1799916</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113230</t>
+          <t>110331</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>174411</t>
+          <t>172317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>220782</t>
+          <t>223710</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>304585</t>
+          <t>303009</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>359896</t>
+          <t>356924</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>463060</t>
+          <t>458699</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0802-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>403447</t>
+          <t>403012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>432304</t>
+          <t>433474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>243561</t>
+          <t>244897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268744</t>
+          <t>270186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>659221</t>
+          <t>657445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>695265</t>
+          <t>694978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>49413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47158</t>
+          <t>46743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55218</t>
+          <t>56891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86257</t>
+          <t>87982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>28352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46625</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321916</t>
+          <t>322322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344600</t>
+          <t>344982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329310</t>
+          <t>330296</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350821</t>
+          <t>351291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>660354</t>
+          <t>660165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691123</t>
+          <t>690561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33973</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12744</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31173</t>
+          <t>31307</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>32516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>57852</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,49 +1430,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9397</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4390</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9397</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4911</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17372</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>17</t>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>456430</t>
+          <t>456155</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>488018</t>
+          <t>486044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115607</t>
+          <t>115290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137504</t>
+          <t>137802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>579257</t>
+          <t>579237</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>618789</t>
+          <t>619156</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65860</t>
+          <t>65801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35212</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60313</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93572</t>
+          <t>94983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>47147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>975736</t>
+          <t>977432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1031052</t>
+          <t>1032201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>545611</t>
+          <t>548662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>590417</t>
+          <t>591612</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1538481</t>
+          <t>1541863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1611094</t>
+          <t>1609310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151963</t>
+          <t>150380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200947</t>
+          <t>199865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97221</t>
+          <t>97958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137052</t>
+          <t>137651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262601</t>
+          <t>260044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>324373</t>
+          <t>321611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45437</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74478</t>
+          <t>73527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18247</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68481</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>102873</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280268</t>
+          <t>280843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307222</t>
+          <t>307497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>431143</t>
+          <t>428526</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>469097</t>
+          <t>469218</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>717515</t>
+          <t>719194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>766594</t>
+          <t>766611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>31573</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>56318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>67407</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102003</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>106004</t>
+          <t>105604</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>148581</t>
+          <t>148189</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>22779</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46343</t>
+          <t>48326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63462</t>
+          <t>62396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>280212</t>
+          <t>280919</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292622</t>
+          <t>292656</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>811630</t>
+          <t>814601</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>877442</t>
+          <t>875711</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1096113</t>
+          <t>1098060</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1165902</t>
+          <t>1166212</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264861</t>
+          <t>260974</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322719</t>
+          <t>320615</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270302</t>
+          <t>269321</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>332715</t>
+          <t>331451</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>93555</t>
+          <t>92199</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133452</t>
+          <t>135296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94091</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>135814</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2773912</t>
+          <t>2776463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2852628</t>
+          <t>2853583</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2546349</t>
+          <t>2540220</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2643706</t>
+          <t>2640786</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5349102</t>
+          <t>5342014</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5471360</t>
+          <t>5476531</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>299572</t>
+          <t>299770</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>368233</t>
+          <t>368884</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>526778</t>
+          <t>526842</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>614332</t>
+          <t>612935</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>846951</t>
+          <t>848109</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>957959</t>
+          <t>967811</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100723</t>
+          <t>100783</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>144069</t>
+          <t>143519</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182690</t>
+          <t>184158</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>241263</t>
+          <t>243474</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>302991</t>
+          <t>296464</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>376670</t>
+          <t>370751</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>364108</t>
+          <t>363179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>393920</t>
+          <t>394088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>262472</t>
+          <t>263423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287167</t>
+          <t>288373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>634585</t>
+          <t>635069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>674896</t>
+          <t>675303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>64888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38892</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56513</t>
+          <t>57820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92661</t>
+          <t>92366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>32114</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354840</t>
+          <t>354760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>382513</t>
+          <t>381601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287229</t>
+          <t>288173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311064</t>
+          <t>311505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>651631</t>
+          <t>649716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>687611</t>
+          <t>686986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46640</t>
+          <t>46217</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>37194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45308</t>
+          <t>45801</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75929</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>21235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>37307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492429</t>
+          <t>489712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533920</t>
+          <t>532142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>173552</t>
+          <t>176037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203645</t>
+          <t>203880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>677077</t>
+          <t>676394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>727977</t>
+          <t>729793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60497</t>
+          <t>58572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95636</t>
+          <t>93836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32595</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58223</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99596</t>
+          <t>100278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143925</t>
+          <t>142975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54421</t>
+          <t>54943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50441</t>
+          <t>50679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84122</t>
+          <t>86440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>915935</t>
+          <t>914236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>971661</t>
+          <t>969242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622456</t>
+          <t>619871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>663817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1551160</t>
+          <t>1551415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1621446</t>
+          <t>1621046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117488</t>
+          <t>117832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164094</t>
+          <t>162039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58925</t>
+          <t>59546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93489</t>
+          <t>94516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186857</t>
+          <t>188386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244914</t>
+          <t>243874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60566</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97006</t>
+          <t>96826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61373</t>
+          <t>61696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102795</t>
+          <t>104189</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148475</t>
+          <t>148767</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>403962</t>
+          <t>403130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>438868</t>
+          <t>438902</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>481496</t>
+          <t>481007</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>533802</t>
+          <t>535718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898410</t>
+          <t>899901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>959542</t>
+          <t>963370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44726</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72254</t>
+          <t>73373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>123063</t>
+          <t>122516</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>168557</t>
+          <t>168092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>177307</t>
+          <t>175341</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>231158</t>
+          <t>229185</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42871</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89988</t>
+          <t>88974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127758</t>
+          <t>129970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117029</t>
+          <t>117787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161268</t>
+          <t>163493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>247058</t>
+          <t>248018</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>261215</t>
+          <t>261051</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>683445</t>
+          <t>679724</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>749439</t>
+          <t>749841</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>938864</t>
+          <t>938432</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1005578</t>
+          <t>1009243</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>221830</t>
+          <t>221204</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>278468</t>
+          <t>280242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>228123</t>
+          <t>226755</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>285583</t>
+          <t>285847</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119891</t>
+          <t>121498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166055</t>
+          <t>167192</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>124780</t>
+          <t>125196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173443</t>
+          <t>171784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2833796</t>
+          <t>2841011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2921935</t>
+          <t>2929634</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2582940</t>
+          <t>2586084</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2689847</t>
+          <t>2688461</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5455665</t>
+          <t>5453989</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5595537</t>
+          <t>5590568</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>326140</t>
+          <t>322490</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>399243</t>
+          <t>399882</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>520873</t>
+          <t>521402</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>611318</t>
+          <t>610714</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>865899</t>
+          <t>867686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>981350</t>
+          <t>980222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>147631</t>
+          <t>145415</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>203894</t>
+          <t>198910</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>310098</t>
+          <t>311287</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>380806</t>
+          <t>384777</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>478828</t>
+          <t>474485</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>567936</t>
+          <t>568948</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>366547</t>
+          <t>363919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392248</t>
+          <t>392940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293165</t>
+          <t>293764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318817</t>
+          <t>318931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>666966</t>
+          <t>665055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>704338</t>
+          <t>704449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>24818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>49673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35203</t>
+          <t>35687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76860</t>
+          <t>76799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23212</t>
+          <t>23939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43871</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324120</t>
+          <t>323815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348720</t>
+          <t>348964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312349</t>
+          <t>312482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339052</t>
+          <t>339400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643011</t>
+          <t>644743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681176</t>
+          <t>683414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>38065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44641</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>40392</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72364</t>
+          <t>72640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23380</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>20721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43202</t>
+          <t>42365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>424278</t>
+          <t>422605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>457520</t>
+          <t>454780</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107318</t>
+          <t>109335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132626</t>
+          <t>133624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>540607</t>
+          <t>538311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>584369</t>
+          <t>581831</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>42072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70493</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44871</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68798</t>
+          <t>70813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103861</t>
+          <t>106889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>931971</t>
+          <t>932281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>982912</t>
+          <t>985017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>676331</t>
+          <t>678108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>720445</t>
+          <t>719249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1623803</t>
+          <t>1626804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1690394</t>
+          <t>1692668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108511</t>
+          <t>107545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>153173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55446</t>
+          <t>55875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86802</t>
+          <t>88415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173812</t>
+          <t>170992</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230591</t>
+          <t>227071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>45217</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78424</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74616</t>
+          <t>74010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97117</t>
+          <t>95325</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141359</t>
+          <t>139960</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>473894</t>
+          <t>471533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>512568</t>
+          <t>511773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>502779</t>
+          <t>503975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>553681</t>
+          <t>554924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>990046</t>
+          <t>987132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1053701</t>
+          <t>1056041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74044</t>
+          <t>74232</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107378</t>
+          <t>110416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107892</t>
+          <t>105941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>151625</t>
+          <t>148001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>192166</t>
+          <t>192873</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>248906</t>
+          <t>248140</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>49237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63910</t>
+          <t>62761</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100315</t>
+          <t>99328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98165</t>
+          <t>96208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140556</t>
+          <t>139867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>273432</t>
+          <t>274403</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>284939</t>
+          <t>284973</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>712468</t>
+          <t>715201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>780041</t>
+          <t>780110</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>992170</t>
+          <t>989173</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1060407</t>
+          <t>1059677</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>178087</t>
+          <t>174806</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>233236</t>
+          <t>231850</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184277</t>
+          <t>180988</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>238334</t>
+          <t>237879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>108000</t>
+          <t>110873</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156252</t>
+          <t>157486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111344</t>
+          <t>112411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>157284</t>
+          <t>160838</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2853013</t>
+          <t>2850292</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2934666</t>
+          <t>2934924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2678696</t>
+          <t>2674890</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2781582</t>
+          <t>2783770</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5557376</t>
+          <t>5547117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5687641</t>
+          <t>5691188</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>301246</t>
+          <t>301110</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>373921</t>
+          <t>375917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>447047</t>
+          <t>444527</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>533230</t>
+          <t>534555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>770009</t>
+          <t>769563</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>874039</t>
+          <t>883242</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>130947</t>
+          <t>130484</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>178352</t>
+          <t>178194</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>281301</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>355343</t>
+          <t>353599</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>426709</t>
+          <t>423926</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>516289</t>
+          <t>517401</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>461326</t>
+          <t>501829</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>447631</t>
+          <t>487733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>470646</t>
+          <t>512609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>394773</t>
+          <t>427075</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>383857</t>
+          <t>415375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>404471</t>
+          <t>438547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>856099</t>
+          <t>928904</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>839928</t>
+          <t>909426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>870086</t>
+          <t>944914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40798</t>
+          <t>43703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>41437</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>32505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45979</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,22 +11189,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>66448</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54845</t>
+          <t>59824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78655</t>
+          <t>90035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23899</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>35076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>26214</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504465</t>
+          <t>549744</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>504465</t>
+          <t>549744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504465</t>
+          <t>549744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951932</t>
+          <t>1038155</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951932</t>
+          <t>1038155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951932</t>
+          <t>1038155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399871</t>
+          <t>427901</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386411</t>
+          <t>414303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411438</t>
+          <t>440243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>327009</t>
+          <t>360911</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315260</t>
+          <t>348622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336599</t>
+          <t>371908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>726881</t>
+          <t>788811</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709011</t>
+          <t>767106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743576</t>
+          <t>804635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42135</t>
+          <t>44565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31939</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54399</t>
+          <t>57281</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37959</t>
+          <t>42286</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>80094</t>
+          <t>86851</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>65086</t>
+          <t>72968</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>96403</t>
+          <t>105767</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -11688,22 +11688,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>40832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>350638</t>
+          <t>393075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139639</t>
+          <t>377387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>560359</t>
+          <t>407669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>122215</t>
+          <t>138536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>128244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130613</t>
+          <t>147761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>472852</t>
+          <t>531611</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218547</t>
+          <t>513024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>675719</t>
+          <t>548385</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>293801</t>
+          <t>54029</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70411</t>
+          <t>42582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>517410</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>31394</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22127</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>39329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>322827</t>
+          <t>85424</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104069</t>
+          <t>72008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>598225</t>
+          <t>102549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44079</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>42074</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>54259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>835133</t>
+          <t>914945</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>808709</t>
+          <t>890163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>860951</t>
+          <t>941540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>852674</t>
+          <t>722192</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>704504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>907711</t>
+          <t>737327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1687805</t>
+          <t>1637137</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1640847</t>
+          <t>1605449</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1791290</t>
+          <t>1667080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>136494</t>
+          <t>149120</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115928</t>
+          <t>126601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158688</t>
+          <t>171680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>97224</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48125</t>
+          <t>83184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114795</t>
+          <t>111950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>223339</t>
+          <t>246344</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152823</t>
+          <t>220099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259125</t>
+          <t>273587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>67778</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49087</t>
+          <t>54245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>83509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38575</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>33510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>52553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>101767</t>
+          <t>109573</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69654</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>123749</t>
+          <t>127267</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>375173</t>
+          <t>460561</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>357728</t>
+          <t>439203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>391972</t>
+          <t>475964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>615467</t>
+          <t>587801</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>577625</t>
+          <t>566004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>670738</t>
+          <t>607901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>990640</t>
+          <t>1048362</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>955644</t>
+          <t>1018673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1049803</t>
+          <t>1076851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65691</t>
+          <t>70890</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52023</t>
+          <t>56348</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>87371</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>136486</t>
+          <t>144272</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100751</t>
+          <t>127922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>163361</t>
+          <t>161508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>202177</t>
+          <t>215162</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>164118</t>
+          <t>194692</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>229613</t>
+          <t>239841</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24769</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44728</t>
+          <t>48356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>89382</t>
+          <t>98777</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66392</t>
+          <t>85455</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106654</t>
+          <t>114228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>123564</t>
+          <t>135291</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98918</t>
+          <t>118198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143026</t>
+          <t>154268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>234776</t>
+          <t>231636</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>228561</t>
+          <t>226008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>238063</t>
+          <t>234869</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>509046</t>
+          <t>571908</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>485753</t>
+          <t>546461</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>529870</t>
+          <t>593900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>743824</t>
+          <t>803544</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>717001</t>
+          <t>778477</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>768249</t>
+          <t>829739</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>156805</t>
+          <t>169293</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140599</t>
+          <t>151831</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176001</t>
+          <t>188997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>160912</t>
+          <t>173189</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143492</t>
+          <t>154180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>182386</t>
+          <t>192766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>94946</t>
+          <t>102502</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82531</t>
+          <t>88591</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>110755</t>
+          <t>119058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,17 +13582,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>96570</t>
+          <t>104199</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81984</t>
+          <t>88272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114137</t>
+          <t>120963</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760797</t>
+          <t>843704</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760797</t>
+          <t>843704</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760797</t>
+          <t>843704</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001305</t>
+          <t>1080932</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001305</t>
+          <t>1080932</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001305</t>
+          <t>1080932</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2656916</t>
+          <t>2929946</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2097795</t>
+          <t>2888666</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2875897</t>
+          <t>2969780</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2821184</t>
+          <t>2808424</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2755702</t>
+          <t>2764788</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2958107</t>
+          <t>2850772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5478101</t>
+          <t>5738369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4782299</t>
+          <t>5685945</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5699311</t>
+          <t>5789946</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>572134</t>
+          <t>355237</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>345671</t>
+          <t>317603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1155742</t>
+          <t>389333</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>483663</t>
+          <t>525907</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>398041</t>
+          <t>492444</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>562078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1055797</t>
+          <t>881143</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>823198</t>
+          <t>839509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1799916</t>
+          <t>927183</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>146262</t>
+          <t>156419</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>110331</t>
+          <t>135154</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>172317</t>
+          <t>180543</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>272338</t>
+          <t>300487</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>223710</t>
+          <t>275841</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>303009</t>
+          <t>329353</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>418600</t>
+          <t>456906</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>356924</t>
+          <t>423832</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>458699</t>
+          <t>495010</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3375313</t>
+          <t>3441602</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3375313</t>
+          <t>3441602</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3375313</t>
+          <t>3441602</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3577184</t>
+          <t>3634817</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3577184</t>
+          <t>3634817</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3577184</t>
+          <t>3634817</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6952498</t>
+          <t>7076418</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6952498</t>
+          <t>7076418</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6952498</t>
+          <t>7076418</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
